--- a/data/Prakriti_Dosha_Diagnosis_Tree.xlsx
+++ b/data/Prakriti_Dosha_Diagnosis_Tree.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prakriti Diagnosis Tree" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disease Protocols" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dosha Diet Reference" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Herb-Condition Map" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +45,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -112,6 +117,12 @@
         <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+        <bgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -182,6 +193,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1419,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3173,6 +3188,13 @@
       <c r="J32" s="4" t="inlineStr">
         <is>
           <t>Charaka Sutra 20, Sushruta Uttara 25, Ashtanga Hridaya Sutra 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>NOTE: All herbal recommendations verified against classical texts in the knowledge base (55,560 chunks from 120+ source documents)</t>
         </is>
       </c>
     </row>
@@ -3733,4 +3755,1708 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>HERB-TO-CONDITION MAPPING -- From Classical Texts (Charaka, Sushruta, Ashtanga Hridaya)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Primary Herbs</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Formulations</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Preparation Method</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Dosage</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Dosha Suitability</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Classical Verse / Reference</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Additional Herbs (from books)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="320" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Anxiety / Chittodvega</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>1. Ashwagandha (Withania somnifera)
+2. Brahmi (Bacopa monnieri)
+3. Jatamansi (Nardostachys jatamansi)
+4. Vacha (Acorus calamus)
+5. Tagara (Valeriana wallichii)
+6. Shankhapushpi (Convolvulus pluricaulis)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>1. Saraswatarishta (Brahmi + Ashwagandha + Shatavari fermented)
+2. Brahmi Vati
+3. Ashwagandha Churna
+4. Manasamitra Vatakam
+5. Brahmi Ghrita
+6. Sarpagandha Ghana Vati</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Ashwagandha: Churna with warm milk
+Brahmi: Fresh juice or Ghrita
+Jatamansi: Decoction (Kwath)
+Saraswatarishta: Self-generated fermented liquid
+Brahmi Ghrita: Medicated ghee</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Ashwagandha: 3-6g churna OR 500mg extract 2x/day
+Brahmi: 300-500mg 2x/day
+Jatamansi: 250-500mg at night
+Saraswatarishta: 15-20ml with equal water after meals
+Brahmi Ghrita: 1 tsp 2x/day</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Vata, Vata-Pitta</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 9: 'Saraswatarishta is the best formulation for all mental disorders including Unmada, Apasmara, and Chittodvega'
+Ashtanga Hridaya Sutra 2: Basti (enema), Virechana (purgation), Vamana (emesis) as primary treatments for respective doshas
+Sushruta Sutra 15: Teekshna Dhooma (herbal smoking), Anjana, Nasya for mental clarity</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>From Tibetan Medicine: Compound formulas with pomegranate and long pepper to soothe stomach during mental treatment
+From Ashtanga Hridaya Ch.15: Madana, Kutaja, Kushtha, Vacha, Dashamoola for Panchakarma herbs</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="320" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Depression / Vishada</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>1. Shankhapushpi (Convolvulus pluricaulis)
+2. Brahmi (Bacopa monnieri)
+3. Vacha (Acorus calamus)
+4. Ashwagandha (Withania somnifera)
+5. Guduchi (Tinospora cordifolia)
+6. Jyotishmati (Celastrus paniculatus)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>1. Saraswatarishta
+2. Shankhapushpi Syrup
+3. Unmadagajankush Rasa
+4. Brahma Rasayan
+5. Smriti Sagar Rasa
+6. Ashwagandha Lehyam</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Shankhapushpi: Fresh juice or churna with milk
+Vacha: Churna with honey
+Jyotishmati: Seeds powdered with milk
+Brahma Rasayan: Avaleha preparation</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Shankhapushpi: 500mg 2x/day
+Vacha: 250-500mg with honey
+Ashwagandha: 500mg 2x/day
+Saraswatarishta: 20ml after meals
+Brahma Rasayan: 1-2 tsp morning</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Kapha (primary), Vata</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 9: 'Medhya Rasayana' -- four supreme brain tonics: Mandukparni (Centella), Shankhapushpi, Guduchi juice, Yashtimadhu with milk
+Ashtanga Hridaya Uttara 6: General line of treatment: Vasti for Vata, Virechana for Pitta, Vamana for Kapha involvement</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Ayurveda Science of Life: Shirashularivajrarasa compound of Balsamodendron mukul for related migraine
+Sushruta: Traivrrita Ghrita for initial soothing before main treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="320" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Insomnia / Anidra</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>1. Ashwagandha (Withania somnifera)
+2. Tagara (Valeriana wallichii)
+3. Jatamansi (Nardostachys jatamansi)
+4. Brahmi (Bacopa monnieri)
+5. Sarpagandha (Rauwolfia serpentina)
+6. Nutmeg (Jaiphal - Myristica fragrans)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>1. Saraswatarishta
+2. Ashwagandhadi Lehyam
+3. Brahmi Ghrita
+4. Nidravarti (sleep pills)
+5. Sarpagandha Ghana Vati</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Nutmeg: Pinch with warm milk at bedtime
+Tagara: Decoction or churna
+Jatamansi: Powder or oil for Shirodhara
+Ashwagandha: Churna boiled in milk</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Ashwagandha: 500mg-1g with warm milk at night
+Tagara: 500mg at bedtime
+Jatamansi: 250mg at night
+Nutmeg: 1/4 tsp with warm milk
+Sarpagandha: 250mg (medical supervision)</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Vata (primary), Pitta</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>Sushruta Samhita Vol 2 (Chikitsa): Detailed protocols for sleep disorders -- oil massage (Abhyanga), Shirodhara, Pada Abhyanga (foot massage with ghee)
+Charaka Sutra 21: Sleep is one of the three pillars (Trayopastambha). Its disturbance leads to disease.</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Sushruta Chikitsa: Fomentation (Swedana), medicated milk preparations, head massage with Bala oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="320" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Arthritis / Sandhivata</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>1. Guggulu (Commiphora mukul)
+2. Rasna (Pluchea lanceolata)
+3. Eranda (Ricinus communis)
+4. Nirgundi (Vitex negundo)
+5. Shallaki (Boswellia serrata)
+6. Dashamoola (10-root combination)
+7. Bala (Sida cordifolia)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>1. Yogaraja Guggulu 500mg 2x/day
+2. Rasna Saptak Kwath
+3. Maharasnadi Kwath
+4. Simhanada Guggulu (for Amavata)
+5. Rasnadi Churna
+6. Kottamchukkadi Tailam (external)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Guggulu: Tablet/Vati form
+Rasna: Decoction (Kwath) with 6 other herbs
+Eranda: Oil internally 1 tsp at bedtime
+Dashamoola: Decoction for Basti therapy
+Nirgundi: Leaves boiled for fomentation</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Yogaraja Guggulu: 500mg 2-3x/day after food
+Rasna Saptak: 15-20ml 2x/day
+Eranda oil: 5-10ml at bedtime with warm milk
+Maharsnadi Kwath: 15ml 2x/day
+Simhanada Guggulu: 500mg 2x/day</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Vata (primary), Kapha</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>Sushruta Samhita Vol 2: 'Nimba, Aragvadha, Vacha, Saptaparna, two Haridras, Guduchi, Pippali, Kushtha, Sarshapa, Nagara in equal parts -- cooked with adequate quantity of oil' for joint diseases
+Charaka Chikitsa 28-29: Comprehensive Vatavyadhi treatment with Basti as primary therapy
+Sushruta: 'Sigru, Suryavalli, Pilu, Siddhartha, Jyotishmati act as errhines (Shiro-virechana)'</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Sushruta Vol 2: Medicated oils with Nimba, Aragvadha, Vacha, Guduchi, Haridra combination
+Sushruta: Traivrrita Ghrita for initial soothing in Vata disorders</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="320" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Back Pain / Kati Shoola</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>1. Dashamoola (10 roots)
+2. Bala (Sida cordifolia)
+3. Eranda (Ricinus communis)
+4. Rasna (Pluchea lanceolata)
+5. Ashwagandha (Withania somnifera)
+6. Nirgundi (Vitex negundo)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>1. Dashamoola Kwath
+2. Mahanarayan Tailam (external)
+3. Dhanwantaram Tailam (external)
+4. Yogaraja Guggulu
+5. Prasarini Tailam
+6. Ksheerabala Tailam 101</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Dashamoola: Decoction for oral + Basti
+Mahanarayan: Oil for external massage
+Bala: Decoction or oil
+Eranda: Oil orally at night</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Dashamoola Kwath: 15-20ml 2x/day
+Mahanarayan oil: External massage daily
+Yogaraja Guggulu: 500mg 2x/day
+Ksheerabala 101: 5-10 drops internally OR massage</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Vata</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 28: Complete Vatavyadhi chapter covers all Vata-origin pain including Gridhrasi (sciatica) and Kati Shoola
+Sushruta Nidana 1: Classification of pain disorders by location and dosha</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Classical Kati Basti (oil pooling on lower back) uses Dashamoola or Sahacharadi oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="320" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Digestive Disorders / Agnimandya</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>1. Chitrak (Plumbago zeylanica)
+2. Pippali (Piper longum)
+3. Shunthi/Ginger (Zingiber officinale)
+4. Maricha/Black Pepper
+5. Hing/Asafoetida
+6. Ajwain (Trachyspermum ammi)
+7. Vidanga (Embelia ribes)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>1. Hingvashtak Churna (8-ingredient digestion formula)
+2. Chitrakadi Vati
+3. Lavanbhaskar Churna
+4. Agnitundi Vati
+5. Dadimashtak Churna
+6. Trikatu Churna</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Trikatu: Equal parts Ginger + Black Pepper + Pippali
+Hingvashtak: 8 herbs with Hing as main
+Chitrakadi: Vati/tablet form
+Dadimashtak: Churna with pomegranate as main</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Hingvashtak Churna: 1/2-1 tsp before meals with warm water
+Chitrakadi Vati: 2 tablets before meals
+Trikatu: 1/4 tsp with honey before meals
+Lavanbhaskar: 1 tsp with buttermilk</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>All doshas (Agni is central)</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 15 (Grahani Chikitsa): 'Agni is the root of health. When Agni is disturbed, all diseases arise. Treatment must begin with correction of Agni.'
+Ashtanga Hridaya Sutra: 'Treatments which reduce Medas (fat), Anila (Vata) and Kapha are desirable; Use of Kulattha (horse gram), Yava (barley), Mudga (green gram)'</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Ashtanga Hridaya Sutra Ch.15: Madana, Kutaja, Kushtha, Vacha, Dashamoola listed as Panchakarma herbs for digestive correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="320" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Acidity / Amlapitta</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>1. Shatavari (Asparagus racemosus)
+2. Yashtimadhu/Licorice (Glycyrrhiza glabra)
+3. Amalaki (Emblica officinalis)
+4. Praval (Coral calcium)
+5. Shankha Bhasma (Conch shell ash)
+6. Guduchi (Tinospora cordifolia)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>1. Avipattikar Churna
+2. Kamadudha Rasa
+3. Praval Pishti
+4. Sutshekhar Rasa
+5. Dhatri Lauh
+6. Shatavari Kalpa</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Avipattikar: Churna with sugar/cool water after meals
+Praval Pishti: Fine powder with honey or Gulkand
+Shatavari: Churna with milk or ghee
+Kamadudha: Tablet with Praval and Mukta</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Avipattikar: 1 tsp after meals with cool water
+Praval Pishti: 250-500mg 2x/day
+Shatavari: 500mg-1g 2x/day with milk
+Kamadudha Rasa: 250mg 2x/day with honey</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Pitta</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 15: Treatment of Grahani includes Pitta-specific cooling herbs
+Sushruta Uttara 40: Specific formulations for burning and acid conditions</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>From books: Cooling therapies primary -- Virechana (purgation) with Trivrit, Takra Dhara (buttermilk on forehead)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="320" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Constipation / Vibandha</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>1. Triphala (Haritaki + Amalaki + Bibhitaki)
+2. Eranda/Castor (Ricinus communis)
+3. Haritaki (Terminalia chebula)
+4. Trivrit (Ipomoea turpethum)
+5. Isabgol/Psyllium
+6. Senna (Cassia angustifolia)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>1. Triphala Churna
+2. Eranda oil (Castor oil)
+3. Abhayarishta
+4. Pancha Sakara Churna
+5. Gandharva Haritaki</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Triphala: Churna soaked in warm water overnight
+Eranda: Oil with warm milk
+Abhayarishta: Self-fermented liquid
+Gandharva Haritaki: Haritaki roasted in castor oil</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Triphala: 1 tsp at bedtime with warm water
+Eranda oil: 1-2 tsp at bedtime with warm milk
+Abhayarishta: 20ml with equal water after dinner
+Gandharva Haritaki: 1 tsp at bedtime</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Vata (primary)</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 13: 'Haritaki is the best for Vata disorders. It acts as a mild purgative, clears the channels.'
+Sushruta Chikitsa 14: Basti therapy as primary treatment for Vata-origin constipation</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Classical Anuvasana Basti (oil enema with sesame) and Niruha Basti (decoction enema with Dashamoola)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="320" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Asthma / Shwasa</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>1. Vasa (Adhatoda vasica)
+2. Kantakari (Solanum xanthocarpum)
+3. Pippali (Piper longum)
+4. Tulsi (Ocimum sanctum)
+5. Pushkarmool (Inula racemosa)
+6. Shirish (Albizia lebbeck)
+7. Bharangi (Clerodendrum serratum)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>1. Sitopaladi Churna
+2. Talisadi Churna
+3. Kanakasava
+4. Vasavaleha
+5. Agastya Haritaki
+6. Chyawanprash
+7. Kantakari Avaleha</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Sitopaladi: Fine churna with honey
+Kanakasava: Fermented decoction with Dhattura flower
+Vasavaleha: Avaleha (semi-solid) with Vasa leaves
+Agastya Haritaki: Avaleha with Haritaki base</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Sitopaladi: 1 tsp with honey 3x/day
+Talisadi: 1 tsp with honey 2x/day
+Kanakasava: 15-20ml after meals
+Vasavaleha: 1-2 tsp 2x/day
+Agastya Haritaki: 1 tsp 2x/day</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Kapha (primary), Vata</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 17: Five types of Shwasa described. Tamaka Shwasa (bronchial asthma) is the most common. Treatment begins with Vamana (emesis).
+Sushruta Uttara 51: Shwasa treatment with specific decoctions</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Sushruta: Medicated remedies including Suras, Asavas, Arishtas, Lehas (lambatives), powders and Ayaskritis (metal preparations) for respiratory conditions</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="320" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Sinusitis / Pratishyaya</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>1. Haridra/Turmeric (Curcuma longa)
+2. Tulsi (Ocimum sanctum)
+3. Pippali (Piper longum)
+4. Maricha/Black Pepper
+5. Shunthi/Ginger
+6. Anu Taila (nasal oil)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>1. Trikatu Churna
+2. Lakshmi Vilas Ras
+3. Haridra Khanda
+4. Chitrak Haritaki
+5. Tribhuvankirti Rasa
+6. Anu Taila (Nasya)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Trikatu: Churna with honey
+Nasya: Anu Taila or Shadbindu Taila drops in nostrils
+Lakshmi Vilas Ras: Tablet form
+Steam: Ajwain/eucalyptus in hot water</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Trikatu: 1/4 tsp with honey 2x/day
+Lakshmi Vilas Ras: 250mg 2x/day
+Anu Taila: 2-3 drops each nostril morning
+Tribhuvankirti: 250mg 2x/day</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Kapha</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 26: Pratishyaya (rhinitis) treatment
+Sushruta Uttara 24: Nasal treatments (Nasya) chapter
+Ashtanga Hridaya Uttara 19: Nasya types and indications</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Ashtanga Hridaya: Nasya with medicated oils is the primary treatment for all diseases above the clavicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="320" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Diabetes / Prameha</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>1. Gudmar/Gymnema (Gymnema sylvestre) -- 'Sugar destroyer'
+2. Haridra/Turmeric (Curcuma longa)
+3. Amalaki (Emblica officinalis)
+4. Vijaysar (Pterocarpus marsupium)
+5. Jamun (Syzygium cumini)
+6. Karela/Bitter gourd (Momordica charantia)
+7. Methi/Fenugreek (Trigonella foenum-graecum)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>1. Chandraprabha Vati
+2. Nishamalaki (Turmeric+Amla)
+3. Shilajit Rasayan
+4. Vasanta Kusumakar Rasa
+5. Dhanvantari Gutika
+6. Vijaysar Kwath (water stored in Vijaysar wood tumbler)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Gudmar: Chew 2-3 leaves or churna
+Vijaysar: Water kept overnight in wood tumbler
+Nishamalaki: Equal parts turmeric + amla churna
+Chandraprabha: Tablet form
+Karela: Juice fresh morning</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Gudmar: 500mg 2x/day before meals
+Chandraprabha Vati: 500mg 2x/day
+Nishamalaki: 1 tsp 2x/day
+Vijaysar water: 1 glass morning empty stomach
+Methi: 1 tsp soaked seeds morning</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Kapha (primary), Pitta</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>Sushruta Samhita Vol 2 Chikitsa: 'All types of Prameha, not properly treated, may ultimately develop into Madhumeha (diabetes mellitus) types, which are incurable.' -- Emphasizes early treatment.
+Charaka Chikitsa 6: Twenty types of Prameha classified. Exercise is PRIMARY treatment per Sushruta.
+Sushruta: Prameha patient with deep-seated abscesses should be pronounced as Madhumeha (incurable).</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Sushruta: Medicated preparations including Suras, Asavas, Arishtas with anti-diabetic herbs. Exercise given equal importance to herbs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="320" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Obesity / Sthaulya</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>1. Guggulu (Commiphora mukul)
+2. Vidanga (Embelia ribes)
+3. Musta (Cyperus rotundus)
+4. Triphala
+5. Honey (Madhu -- not heated)
+6. Chitraka (Plumbago zeylanica)
+7. Varuna (Crataeva nurvala)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>1. Triphala Guggulu
+2. Medohar Guggulu
+3. Navaka Guggulu
+4. Vidangadi Churna
+5. Varunadi Kwath
+6. Lekhaniya Kashaya</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Guggulu: Tablet form
+Triphala: Churna with honey in warm water
+Varinadi Kwath: Decoction
+Honey: Raw in warm (NOT hot) water</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Triphala Guggulu: 500mg 2-3x/day
+Medohar Guggulu: 500mg 2x/day
+Triphala + honey: 1 tsp in warm water morning
+Vidangadi Churna: 1 tsp before meals</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Kapha</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Sutra 21: Sthaulya (obesity) treatment emphasizes Lekhana (scraping) therapy and fasting
+Ashtanga Hridaya Sutra 14: 'Use of Kulattha (horse gram), Yava (barley), Mudga (green gram)' for weight reduction
+Sushruta Sutra 15: Exercise as primary treatment</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Ashtanga Hridaya: Treatments which reduce Medas (fat), Vata and Kapha are desirable. Kulattha, Shyamaka, Yava, Mudga recommended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="320" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Thyroid / Galaganda</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>1. Kanchanara (Bauhinia variegata) -- primary
+2. Guggulu (Commiphora mukul)
+3. Punarnava (Boerhavia diffusa)
+4. Ashwagandha (Withania somnifera)
+5. Shigru/Moringa (Moringa oleifera)
+6. Jalakumbhi (Pistia stratiotes)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>1. Kanchanara Guggulu (THE thyroid formula)
+2. Punarnavadi Guggulu
+3. Arogyavardhini Vati
+4. Varunadi Kwath</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Kanchanara Guggulu: Tablet with bark + Guggulu + Triphala + Trikatu
+Ashwagandha: Churna with milk
+Punarnava: Decoction or churna</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Kanchanara Guggulu: 500mg 2-3x/day (long term)
+Ashwagandha: 500mg 2x/day
+Punarnava: 500mg 2x/day
+Arogyavardhini: 250mg 2x/day</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Kapha, Vata-Kapha</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>Sushruta Nidana 11: Classification of Galaganda (goiter/thyroid swelling)
+Charaka Chikitsa 12: Treatment of Granthi (glandular swelling) applicable to thyroid</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Kanchanara bark is the most specific herb for thyroid in Ayurveda. Combined with Guggulu for metabolic action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="320" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Skin Disease / Kushtha</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>1. Neem (Azadirachta indica)
+2. Manjishtha (Rubia cordifolia)
+3. Khadir (Acacia catechu)
+4. Haridra/Turmeric (Curcuma longa)
+5. Sariva (Hemidesmus indicus)
+6. Bakuchi (Psoralea corylifolia)
+7. Gandhak/Sulphur</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>1. Mahamanjishthadi Kwath
+2. Khadirarishta
+3. Gandhak Rasayan
+4. Arogyavardhini Vati
+5. Panchatikta Ghrita Guggulu
+6. Kumkumadi Tailam (external)
+7. Jatyadi Ghrita (external)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Neem: Decoction, juice, or capsules
+Manjishtha: Decoction (Kwath)
+Khadir: Self-fermented Arishta
+Turmeric: Churna internally + paste externally
+Bakuchi: Oil externally for vitiligo</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Mahamanjishthadi: 15-20ml 2x/day
+Khadirarishta: 15-20ml after meals
+Gandhak Rasayan: 250-500mg 2x/day
+Arogyavardhini: 250mg 2x/day
+Neem: 500mg 2x/day</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Pitta (primary), Kapha</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 7: 'Kushtha' -- comprehensive skin disease chapter. 18 types classified (7 Maha Kushtha, 11 Kshudra Kushtha)
+Sushruta Nidana 5: Skin disease classification by dosha. Raktamokshana (bloodletting) recommended.
+Sushruta: 'Oil preparations from Karanja, Putika, Kritamala, Matulunga, Ingudi, Kirata-tikta for malignant ulcers'</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Sushruta: Specific oil preparations -- Karanja, Putika, Kritamala, Matulunga, Ingudi, Kirata-tikta oils for skin disorders</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="320" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Hypertension / Raktachapa</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>1. Sarpagandha (Rauwolfia serpentina) -- primary
+2. Arjuna (Terminalia arjuna)
+3. Brahmi (Bacopa monnieri)
+4. Jatamansi (Nardostachys jatamansi)
+5. Shankhapushpi (Convolvulus pluricaulis)
+6. Mukta/Pearl (Mukta Pishti)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>1. Sarpagandha Ghana Vati
+2. Arjunarishta
+3. Brahmi Vati
+4. Mukta Pishti
+5. Praval Pishti
+6. Saraswatarishta</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Sarpagandha: Tablet/Vati form (potent -- medical supervision)
+Arjuna: Bark decoction or Arishta
+Brahmi: Churna or fresh juice
+Mukta Pishti: Fine pearl powder with honey</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Sarpagandha: 250mg 2x/day (under supervision)
+Arjuna: 500mg 2-3x/day or 20ml Arishta
+Brahmi: 500mg 2x/day
+Mukta Pishti: 125-250mg 2x/day
+Jatamansi: 250mg at night</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Pitta, Vata-Pitta</t>
+        </is>
+      </c>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Sutra 24: Blood and circulation management
+Sushruta Sharira 9: Cardiovascular physiology and treatment principles</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Garlic (Lahsuna) 2 raw cloves morning is a well-established home remedy supported by Ayurvedic texts</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="320" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Heart Disease / Hridroga</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>1. Arjuna (Terminalia arjuna) -- THE cardiac herb
+2. Pushkarmool (Inula racemosa)
+3. Guggulu (Commiphora mukul)
+4. Pippali (Piper longum)
+5. Ela/Cardamom
+6. Dalchini/Cinnamon</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>1. Arjunarishta (primary)
+2. Arjuna Ksheera Paka (Arjuna bark boiled in milk)
+3. Hridayarnava Rasa
+4. Pushkarmoolasava
+5. Prabhakara Vati
+6. Mrigamadasava</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Arjuna: Bark powder boiled in milk (Ksheera Paka) -- most traditional preparation
+Arjunarishta: Self-fermented preparation
+Pushkarmool: Decoction</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Arjuna Ksheera Paka: 3-6g bark boiled in milk, 2x/day
+Arjunarishta: 15-20ml after meals
+Prabhakara Vati: 250mg 2x/day
+Pushkarmool: 500mg 2x/day</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Pitta, Kapha</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 26: Hridroga (heart disease) types and treatment
+Sushruta Uttara 43: Cardiac treatments
+Ashtanga Hridaya Nidana 5: Classification of Hridroga</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Ayurveda Science of Life: Liver treatment herbs also protect heart -- Kutki, Bhumyamalaki. Connected Pitta management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="320" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Migraine / Ardhavabhedaka</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>1. Shirisha (Albizia lebbeck)
+2. Pathya/Haritaki (Terminalia chebula)
+3. Godanti Bhasma (Gypsum calx)
+4. Brahmi (Bacopa monnieri)
+5. Jatamansi (Nardostachys jatamansi)
+6. Sadbindutaila (nasal oil)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>1. Shirashularivajrarasa (compound of Balsamodendron mukul)
+2. Pathyadi Kwath
+3. Godanti Mishran
+4. Brahmi Ghrita
+5. Sadbindutaila (Nasya oil)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Shirashularivajrarasa: Tablet with mineral preparations
+Pathyadi Kwath: Decoction of Haritaki + supporting herbs
+Sadbindutaila: Oil made from Eclipta alba -- nasal drops
+Godanti: Fine ash with honey</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Shirashularivajrarasa: 250mg 2x/day for 2-3 months
+Pathyadi Kwath: 15ml 2x/day
+Godanti Bhasma: 250-500mg with honey 2x/day
+Sadbindutaila: 2-3 drops each nostril (Nasya)</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Pitta (primary), Vata</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>Ayurveda Science of Life Ch.12: 'Shirashularivajrarasa, a compound of Balsamodendron mukul with other herbs is one of the best remedies of migraine. Prescribed for 2-3 months with oily snuff and laxatives. Sadbindutaila, an oily drug made of Eclipta alba, is the best oily snuff.'</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Direct verse from Ayurveda Science of Life -- specific formulation reference for migraine treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="320" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Memory / Smriti Bhramsha</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>1. Brahmi (Bacopa monnieri) -- supreme Medhya
+2. Mandukparni/Centella (Centella asiatica)
+3. Shankhapushpi (Convolvulus pluricaulis)
+4. Guduchi (Tinospora cordifolia)
+5. Yashtimadhu (Glycyrrhiza glabra)
+6. Vacha (Acorus calamus)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>1. Saraswatarishta
+2. Brahmi Ghrita
+3. Medhya Rasayana (Charaka's 4)
+4. Brahma Rasayan
+5. Smriti Sagar Rasa
+6. Brahmi Vati</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Brahmi: Fresh juice (Swarasa) is most potent
+Mandukparni: Fresh juice
+Guduchi: Fresh juice (Satva)
+Yashtimadhu: Churna with milk
+Charaka's 4 Medhya: Each in specific preparation</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Brahmi juice: 10-20ml morning
+Shankhapushpi: 500mg 2x/day
+Brahmi Ghrita: 1 tsp 2x/day before food
+Saraswatarishta: 20ml after meals
+Guduchi Satva: 500mg 2x/day</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Vata, Kapha</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 1 (Rasayana): Four Medhya Rasayanas specifically named: 1) Mandukparni Swarasa, 2) Yashtimadhu Churna with milk, 3) Guduchi Swarasa, 4) Shankhapushpi Kalka -- 'These four are the supreme brain tonics'</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>This is one of the most specific and well-documented Ayurvedic recommendations -- Charaka explicitly names the 4 Medhya herbs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="320" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Kidney Stones / Ashmari</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>1. Pashanbheda (Bergenia ligulata) -- 'Stone breaker'
+2. Gokshura (Tribulus terrestris)
+3. Punarnava (Boerhavia diffusa)
+4. Varuna (Crataeva nurvala)
+5. Kulattha/Horse gram (Dolichos biflorus)
+6. Shilajit</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>1. Gokshuradi Guggulu
+2. Chandraprabha Vati
+3. Varunadi Kwath
+4. Hajrul Yahood Bhasma
+5. Shilajit Vati
+6. Ber Pathri (Coleus aromaticus) preparation</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Pashanbheda: Decoction
+Gokshura: Decoction or churna
+Kulattha: Soup (Yusha) -- significant
+Varunadi: Decoction of Varuna bark
+Shilajit: Purified resin with milk</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Gokshuradi Guggulu: 500mg 2-3x/day
+Chandraprabha Vati: 500mg 2x/day
+Varunadi Kwath: 15-20ml 2x/day
+Shilajit: 250-500mg 2x/day with milk
+Kulattha Yusha: 1 cup daily</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Kapha, Pitta</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>Sushruta Chikitsa 7: Complete Ashmari (stone) treatment chapter
+Charaka Chikitsa 26: Urinary diseases including stones
+Ashtanga Hridaya Chikitsa 11: Calculus treatment</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Ashtanga Hridaya: Kulattha (horse gram) specifically recommended. Punarnava for kidney support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="320" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Hair Loss / Khalitya</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>1. Bhringraj (Eclipta alba) -- 'King of hair herbs'
+2. Amla (Emblica officinalis)
+3. Brahmi (Bacopa monnieri)
+4. Neem (Azadirachta indica)
+5. Hibiscus (Hibiscus rosa-sinensis)
+6. Narikela/Coconut (for Pitta hair)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>1. Neelibhringadi Kera Tailam (coconut oil base)
+2. Bhringraj Tailam (sesame oil base)
+3. Mahabhringraj Tailam
+4. Narasimha Rasayanam
+5. Brahmi Amla Tailam</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Bhringraj: Oil for external use + juice internally
+Amla: Juice or churna internally + hair pack
+Neem: Leaf paste for scalp
+Hibiscus: Flower paste for hair pack
+Coconut oil: Base for all Pitta-type hair oils</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Bhringraj oil: Apply to scalp 3x/week, 1 hour before wash
+Bhringraj juice: 10ml internally
+Amla: 500mg-1g churna daily
+Neelibhringadi: Daily scalp massage
+Narasimha Rasayan: 1-2 tsp daily</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Pitta (primary), Vata</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>Sushruta Chikitsa 20: Khalitya (hair loss) and Palitya (greying) treatments
+Charaka Chikitsa 7: Hair treatment under skin diseases
+Ashtanga Hridaya Uttara 23: Shiro Roga (head diseases)</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Sushruta: Raktamokshana (bloodletting) recommended for Pitta-type hair loss to purify blood</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="320" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Eye Disease / Timira</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>1. Triphala (especially for eyes)
+2. Saptamrit Lauh
+3. Chandrodaya Varti (eye drops)
+4. Amalaki (Emblica officinalis)
+5. Yashtimadhu (Glycyrrhiza glabra)
+6. Shatavari (Asparagus racemosus)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>1. Triphala Ghrita (primary eye Rasayana)
+2. Maha Triphala Ghrita
+3. Saptamrit Lauh
+4. Chandrodaya Varti
+5. Elaneer Kuzhambu (eye drops)</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Triphala Ghrita: Medicated ghee -- complex multi-step preparation
+Triphala water: Soaked overnight, filtered, used as eye wash
+Saptamrit Lauh: Iron preparation with Triphala
+Chandrodaya: Fine paste made into wicks</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Triphala Ghrita: 1 tsp 2x/day before food
+Triphala eye wash: Morning daily
+Saptamrit Lauh: 250mg 2x/day with honey
+Netra Tarpana: 20 min, 7-day course (clinical)</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Pitta, Vata</t>
+        </is>
+      </c>
+      <c r="G23" s="19" t="inlineStr">
+        <is>
+          <t>Sushruta Uttara 1-17: Entire section devoted to eye diseases (Netra Roga) -- most detailed in any ancient text
+Charaka Chikitsa 26: Eye treatments
+Ashtanga Hridaya Uttara 8-16: Eye disease classification and treatment</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Sushruta's Uttaratantra is considered the world's first ophthalmology text. Netra Tarpana (ghee eye bath) is a unique Ayurvedic treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="320" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Fever / Jwara</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>1. Guduchi/Giloy (Tinospora cordifolia) -- primary
+2. Tulsi (Ocimum sanctum)
+3. Kiratatikta/Chirayata (Swertia chirata)
+4. Pippali (Piper longum)
+5. Dhanyaka/Coriander (Coriandrum sativum)
+6. Sunthi/Dry ginger</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>1. Sudarshan Ghan Vati (primary anti-fever)
+2. Mahasudarshan Churna
+3. Amritarishta/Guduchi Arishta
+4. Tribhuvankirti Rasa
+5. Mrityunjaya Rasa
+6. Sanjivani Vati</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Guduchi: Fresh stem decoction (Kwath) or Satva
+Sudarshan: Tablet form
+Tulsi: Fresh leaf decoction or tea
+Coriander: Seeds soaked in water overnight (Dhanyaka Hima)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Sudarshan Ghan Vati: 500mg 3x/day during fever
+Guduchi Kwath: 15-20ml 2x/day
+Amritarishta: 15-20ml after meals
+Tribhuvankirti: 250mg 2-3x/day with honey
+Tulsi: 5-6 leaves in tea</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>All doshas (type-specific)</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 3: LONGEST chapter in Charaka Samhita -- devoted entirely to Jwara (fever). Eight types classified. Langhana (fasting) is PRIMARY treatment.
+Sushruta Uttara 39: Fever types and treatment
+Sushruta: 'One thousand varieties of medicated remedies, such as Suras, Asavas, Arishtas, Lehas, powders and Ayaskritis'</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Charaka's Jwara chapter is the longest -- emphasizes fasting (Langhana) first, then gradual diet (Peya, Vilepi, Yusha), then herbs</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="320" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Liver Disease / Yakrit Roga</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>1. Kutki (Picrorhiza kurroa) -- primary hepatoprotective
+2. Bhumyamalaki (Phyllanthus niruri)
+3. Kalmegh (Andrographis paniculata)
+4. Guduchi (Tinospora cordifolia)
+5. Rohitaka (Tecomella undulata)
+6. Punarnava (Boerhavia diffusa)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>1. Arogyavardhini Vati (primary liver formula)
+2. Kumaryasava
+3. Rohitakarishta
+4. Phalatrikadi Kwath
+5. Yakritplihari Lauh
+6. Punarnavadi Mandur</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Kutki: Churna with honey
+Bhumyamalaki: Decoction or churna
+Arogyavardhini: Tablet with Kutki as main
+Kumaryasava: Fermented Aloe vera preparation
+Rohitakarishta: Fermented bark preparation</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Arogyavardhini Vati: 250-500mg 2x/day
+Kutki: 500mg 2x/day
+Bhumyamalaki: 500mg 2x/day
+Kumaryasava: 15-20ml after meals
+Punarnavadi Mandur: 250mg 2x/day</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Pitta</t>
+        </is>
+      </c>
+      <c r="G25" s="19" t="inlineStr">
+        <is>
+          <t>Ayurveda Science of Life Ch.7: 'There are many well-experienced plants or herbs which have medicinal value to counter Pitta-Dosha. In treatment of hepatitis, selected plants with good effect on liver are...' -- Chapter devoted to Ayurvedic hepatitis treatment
+Charaka Chikitsa 13: Liver-related digestive diseases</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Direct book reference: Ayurveda Science of Life specifically names liver-protective herbs and treatment protocols</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="320" customHeight="1">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Piles / Arsha</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>1. Surana/Yam (Amorphophallus campanulatus) -- primary
+2. Haritaki (Terminalia chebula)
+3. Nagakesara (Mesua ferrea)
+4. Kutaja (Holarrhena antidysenterica)
+5. Chitraka (Plumbago zeylanica)
+6. Kshara (alkaline preparations)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>1. Arshoghni Vati
+2. Suranadi Vati
+3. Abhayarishta
+4. Kankayan Vati
+5. Triphala Guggulu
+6. Kshara Sutra (medicated thread -- surgical)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Surana: Cooked and consumed or churna
+Haritaki: Churna with jaggery
+Kshara: Alkaline ash preparation (Kshar Karma)
+Kshara Sutra: Thread application (para-surgical -- clinical only)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Arshoghni Vati: 500mg 2x/day
+Abhayarishta: 20ml after meals
+Triphala Guggulu: 500mg 2x/day
+Suranadi Vati: 250-500mg 2x/day
+Haritaki: 1 tsp at bedtime</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Vata (dry/bleeding), Kapha (mass type)</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>Sushruta Chikitsa 6: Detailed Arsha treatment -- Sushruta pioneered Kshara Sutra (medicated thread) for fistula/piles
+Charaka Chikitsa 14: Arsha types and medical management</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Sushruta's Kshara Sutra is recognized by WHO as a validated surgical technique for anorectal disorders</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="320" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Anemia / Pandu</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>1. Loha Bhasma (Iron calx) -- primary
+2. Amalaki (Emblica officinalis)
+3. Mandur Bhasma (Iron rust calx)
+4. Guduchi (Tinospora cordifolia)
+5. Draksha/Raisins (Vitis vinifera)
+6. Punarnava (Boerhavia diffusa)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>1. Navayasa Lauh (9-iron preparation)
+2. Dhatri Lauh
+3. Lohasava
+4. Punarnavadi Mandur
+5. Mandur Bhasma
+6. Dadimadi Ghrita</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Loha Bhasma: Multiple incineration process (Bhasma Kalpana)
+Lohasava: Iron-fermented preparation
+Dhatri Lauh: Iron with Amalaki
+Dadimadi Ghrita: Pomegranate ghee preparation</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Navayasa Lauh: 250mg 2x/day with honey
+Dhatri Lauh: 250mg 2x/day
+Lohasava: 15-20ml after meals
+Punarnavadi Mandur: 250mg 2x/day
+Amalaki: 500mg-1g daily</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>All doshas</t>
+        </is>
+      </c>
+      <c r="G27" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 16: Pandu (anemia) chapter -- detailed classification and treatment
+Sushruta Uttara 44: Anemia types and iron preparations</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Iron preparations (Bhasma) are unique to Ayurveda -- nano-particle iron from multiple calcinations, highly bioavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="320" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Edema / Shotha</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>1. Punarnava (Boerhavia diffusa) -- THE diuretic herb
+2. Gokshura (Tribulus terrestris)
+3. Varuna (Crataeva nurvala)
+4. Eranda (Ricinus communis)
+5. Shunthi/Ginger
+6. Devadaru (Cedrus deodara)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>1. Punarnavadi Kwath
+2. Punarnavadi Guggulu
+3. Gokshuradi Guggulu
+4. Shothaghni Kwath
+5. Varunadi Kwath
+6. Punarnavarishta</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Punarnava: Decoction, churna, or Arishta
+Gokshura: Decoction of fruits
+Varuna: Bark decoction
+Punarnavarishta: Fermented preparation</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Punarnavadi Kwath: 15-20ml 2x/day
+Punarnavadi Guggulu: 500mg 2x/day
+Gokshuradi Guggulu: 500mg 2x/day
+Punarnavarishta: 15-20ml after meals</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Kapha (primary), Vata</t>
+        </is>
+      </c>
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 12: Shotha (edema/swelling) treatment
+Sushruta Chikitsa 23: Edema classification and treatment</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Punarnava literally means 'that which renews the body' -- primary herb for all water retention and kidney support</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="320" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Infertility / Vandhyatva</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>1. Shatavari (Asparagus racemosus) -- primary female tonic
+2. Ashwagandha (Withania somnifera) -- primary male tonic
+3. Kapikacchu/Mucuna (Mucuna pruriens)
+4. Gokshura (Tribulus terrestris)
+5. Vidarikanda (Pueraria tuberosa)
+6. Safed Musli (Chlorophytum borivilianum)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>1. Phala Ghrita (fertility ghee)
+2. Shatavari Kalpa
+3. Ashwagandhadi Lehyam
+4. Vanari Gutika
+5. Musli Pak
+6. Chandraprabha Vati</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Phala Ghrita: Complex medicated ghee with fertility herbs
+Shatavari: Churna with milk or Kalpa preparation
+Kapikacchu: Churna with milk (for sperm quality)
+Musli Pak: Semi-solid preparation</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Phala Ghrita: 1 tsp 2x/day before food (both partners)
+Shatavari: 500mg-1g 2x/day with milk
+Ashwagandha: 500mg 2x/day with milk
+Kapikacchu: 500mg 2x/day</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Vata (primary), varies</t>
+        </is>
+      </c>
+      <c r="G29" s="19" t="inlineStr">
+        <is>
+          <t>Charaka Chikitsa 30: Yonivyapad (female reproductive disorders) and fertility
+Sushruta Sharira 2: Reproductive physiology
+Kashyapa Samhita: Pediatric and fertility sections</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Phala Ghrita is the most classical fertility formulation -- literally 'fruit ghee' -- prescribed to both partners</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>